--- a/samples/wildling/기획데이터/Const.xlsx
+++ b/samples/wildling/기획데이터/Const.xlsx
@@ -225,7 +225,7 @@
     <t xml:space="preserve">AdDoubleTargets</t>
   </si>
   <si>
-    <t xml:space="preserve">string</t>
+    <t xml:space="preserve">string[]</t>
   </si>
   <si>
     <t xml:space="preserve">gold;food;material</t>
@@ -988,7 +988,7 @@
   <cols>
     <col min="1" max="1" width="21.09375" customWidth="1"/>
     <col min="2" max="2" width="19.921875" customWidth="1"/>
-    <col min="3" max="3" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="11.71875" customWidth="1"/>
     <col min="4" max="5" width="23.4375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1075,7 +1075,7 @@
   <cols>
     <col min="1" max="1" width="22.265625" customWidth="1"/>
     <col min="2" max="2" width="19.921875" customWidth="1"/>
-    <col min="3" max="3" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="11.71875" customWidth="1"/>
     <col min="4" max="4" width="22.265625" customWidth="1"/>
     <col min="5" max="5" width="21.09375" customWidth="1"/>
   </cols>
